--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97600</v>
+        <v>97601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,48 +884,61 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136391068</v>
+        <v>136447613</v>
       </c>
       <c r="B4" t="n">
-        <v>8452</v>
+        <v>41095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>102007</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Backvickermal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Xystophora carchariella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Zeller, 1839)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västra Konungehultet, Västra Konungehultet, Sm</t>
+          <t>Östra Konungehultet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570241</v>
+        <v>570228</v>
       </c>
       <c r="R4" t="n">
-        <v>6316233</v>
+        <v>6316094</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +972,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Larv i hopspunna blad av backvicker. Bilder granskade av Nils Ryrholm.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -968,6 +981,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -984,6 +998,113 @@
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136447613</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136391068</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Västra Konungehultet, Västra Konungehultet, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570241</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6316233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Långemåla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136391068</t>
         </is>
@@ -994,6 +1115,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96913</v>
+        <v>96926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97601</v>
+        <v>97614</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136447613</v>
       </c>
       <c r="B4" t="n">
-        <v>41095</v>
+        <v>41108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58017-2025 artfynd.xlsx
+++ b/artfynd/A 58017-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136391029</v>
       </c>
       <c r="B2" t="n">
-        <v>96926</v>
+        <v>96927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136391124</v>
       </c>
       <c r="B3" t="n">
-        <v>97614</v>
+        <v>97615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
